--- a/Thesis Forecasting/PAPER CONTEXT/tables/appendix_B_complete_feature_list_by_plant.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/appendix_B_complete_feature_list_by_plant.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature Groups'!$A$1:$D$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Agus 1 Features'!$A$1:$A$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Agus 2 Features'!$A$1:$A$170</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Agus 4 Features'!$A$1:$A$170</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Agus 5 Features'!$A$1:$A$169</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Agus 6 Features'!$A$1:$A$172</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Agus 7 Features'!$A$1:$A$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Agus 1 Features'!$A$1:$A$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Agus 2 Features'!$A$1:$A$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Agus 4 Features'!$A$1:$A$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Agus 5 Features'!$A$1:$A$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Agus 6 Features'!$A$1:$A$277</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Agus 7 Features'!$A$1:$A$214</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A159"/>
+  <dimension ref="A1:A204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1217,754 +1217,1069 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>out_agus1_unit1</t>
+          <t>gen_agus1_unit1_current</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>out_agus1_unit2</t>
+          <t>gen_agus1_unit1_share_current</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>agus1_units_running</t>
+          <t>gen_agus1_unit1_lag1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>agus1_plant_available</t>
+          <t>gen_agus1_unit1_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tot_agus1_gate</t>
+          <t>gen_agus1_unit1_lag2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>elev_agus1</t>
+          <t>gen_agus1_unit1_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tot_agus1</t>
+          <t>gen_agus1_unit1_lag3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag1</t>
+          <t>gen_agus1_unit1_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag3</t>
+          <t>gen_agus1_unit1_lag6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag6</t>
+          <t>gen_agus1_unit1_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag12</t>
+          <t>gen_agus1_unit1_lag12</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag24</t>
+          <t>gen_agus1_unit1_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>elev_agus1_lag1</t>
+          <t>gen_agus1_unit1_lag24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>elev_agus1_lag3</t>
+          <t>gen_agus1_unit1_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>elev_agus1_lag6</t>
+          <t>gen_agus1_unit1_lag48</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>elev_agus1_lag12</t>
+          <t>gen_agus1_unit1_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>elev_agus1_lag24</t>
+          <t>gen_agus1_unit1_lag72</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tot_agus1_lag1</t>
+          <t>gen_agus1_unit1_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tot_agus1_lag3</t>
+          <t>gen_agus1_unit1_lag168</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tot_agus1_lag6</t>
+          <t>gen_agus1_unit1_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tot_agus1_lag12</t>
+          <t>gen_agus1_unit2_current</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tot_agus1_lag24</t>
+          <t>gen_agus1_unit2_share_current</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag1</t>
+          <t>gen_agus1_unit2_lag1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag3</t>
+          <t>gen_agus1_unit2_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag6</t>
+          <t>gen_agus1_unit2_lag2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag12</t>
+          <t>gen_agus1_unit2_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag24</t>
+          <t>gen_agus1_unit2_lag3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag1</t>
+          <t>gen_agus1_unit2_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag3</t>
+          <t>gen_agus1_unit2_lag6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag6</t>
+          <t>gen_agus1_unit2_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag12</t>
+          <t>gen_agus1_unit2_lag12</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag24</t>
+          <t>gen_agus1_unit2_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag1</t>
+          <t>gen_agus1_unit2_lag24</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag3</t>
+          <t>gen_agus1_unit2_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag6</t>
+          <t>gen_agus1_unit2_lag48</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag12</t>
+          <t>gen_agus1_unit2_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag24</t>
+          <t>gen_agus1_unit2_lag72</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag1</t>
+          <t>gen_agus1_unit2_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag3</t>
+          <t>gen_agus1_unit2_lag168</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag6</t>
+          <t>gen_agus1_unit2_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag12</t>
+          <t>out_agus1_unit1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag24</t>
+          <t>out_agus1_unit2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag1</t>
+          <t>agus1_units_running</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag3</t>
+          <t>agus1_plant_available</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag6</t>
+          <t>tot_agus1_gate</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag12</t>
+          <t>elev_agus1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag24</t>
+          <t>tot_agus1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>elev_agus2_lag1</t>
+          <t>tot_agus1_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>elev_agus2_lag3</t>
+          <t>tot_agus1_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>elev_agus2_lag6</t>
+          <t>tot_agus1_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>elev_agus2_lag12</t>
+          <t>tot_agus1_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>elev_agus2_lag24</t>
+          <t>tot_agus1_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>elev_agus4_lag1</t>
+          <t>elev_agus1_lag1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>elev_agus4_lag3</t>
+          <t>elev_agus1_lag3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>elev_agus4_lag6</t>
+          <t>elev_agus1_lag6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>elev_agus4_lag12</t>
+          <t>elev_agus1_lag12</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>elev_agus4_lag24</t>
+          <t>elev_agus1_lag24</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>elev_agus5_lag1</t>
+          <t>tot_agus1_lag1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>elev_agus5_lag3</t>
+          <t>tot_agus1_lag3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>elev_agus5_lag6</t>
+          <t>tot_agus1_lag6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>elev_agus5_lag12</t>
+          <t>tot_agus1_lag12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>elev_agus5_lag24</t>
+          <t>tot_agus1_lag24</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>elev_agus6_lag1</t>
+          <t>tot_agus2_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>elev_agus6_lag3</t>
+          <t>tot_agus2_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>elev_agus6_lag6</t>
+          <t>tot_agus2_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>elev_agus6_lag12</t>
+          <t>tot_agus2_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>elev_agus6_lag24</t>
+          <t>tot_agus2_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>elev_agus7_lag1</t>
+          <t>tot_agus4_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>elev_agus7_lag3</t>
+          <t>tot_agus4_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>elev_agus7_lag6</t>
+          <t>tot_agus4_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>elev_agus7_lag12</t>
+          <t>tot_agus4_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>elev_agus7_lag24</t>
+          <t>tot_agus4_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag1</t>
+          <t>tot_agus5_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag3</t>
+          <t>tot_agus5_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag6</t>
+          <t>tot_agus5_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag12</t>
+          <t>tot_agus5_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag24</t>
+          <t>tot_agus5_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>tot_agus2_lag1</t>
+          <t>tot_agus6_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>tot_agus2_lag3</t>
+          <t>tot_agus6_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tot_agus2_lag6</t>
+          <t>tot_agus6_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>tot_agus2_lag12</t>
+          <t>tot_agus6_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>tot_agus2_lag24</t>
+          <t>tot_agus6_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>tot_agus4_lag1</t>
+          <t>tot_agus7_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>tot_agus4_lag3</t>
+          <t>tot_agus7_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>tot_agus4_lag6</t>
+          <t>tot_agus7_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>tot_agus4_lag12</t>
+          <t>tot_agus7_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>tot_agus4_lag24</t>
+          <t>tot_agus7_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>tot_agus5_lag1</t>
+          <t>elev_agus2_lag1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tot_agus5_lag3</t>
+          <t>elev_agus2_lag3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tot_agus5_lag6</t>
+          <t>elev_agus2_lag6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tot_agus5_lag12</t>
+          <t>elev_agus2_lag12</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tot_agus5_lag24</t>
+          <t>elev_agus2_lag24</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tot_agus6_lag1</t>
+          <t>elev_agus4_lag1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tot_agus6_lag3</t>
+          <t>elev_agus4_lag3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tot_agus6_lag6</t>
+          <t>elev_agus4_lag6</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tot_agus6_lag12</t>
+          <t>elev_agus4_lag12</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tot_agus6_lag24</t>
+          <t>elev_agus4_lag24</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tot_agus7_lag1</t>
+          <t>elev_agus5_lag1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tot_agus7_lag3</t>
+          <t>elev_agus5_lag3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tot_agus7_lag6</t>
+          <t>elev_agus5_lag6</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tot_agus7_lag12</t>
+          <t>elev_agus5_lag12</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tot_agus7_lag24</t>
+          <t>elev_agus5_lag24</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+          <t>elev_agus6_lag1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+          <t>elev_agus6_lag3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+          <t>elev_agus6_lag6</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+          <t>elev_agus6_lag12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>elev_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>rainfall_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>rainfall_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>rainfall_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>rainfall_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>rainfall_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
           <t>lake_lanao_hourly_outflow_elev_agus7_lag24</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A159"/>
+  <autoFilter ref="A1:A204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1975,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A170"/>
+  <dimension ref="A1:A235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2418,761 +2733,1216 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>out_agus2_unit1</t>
+          <t>gen_agus2_unit1_current</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>out_agus2_unit2</t>
+          <t>gen_agus2_unit1_share_current</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>out_agus2_unit3</t>
+          <t>gen_agus2_unit1_lag1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>agus2_units_running</t>
+          <t>gen_agus2_unit1_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>agus2_plant_available</t>
+          <t>gen_agus2_unit1_lag2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tot_agus2_gate</t>
+          <t>gen_agus2_unit1_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>elev_agus2</t>
+          <t>gen_agus2_unit1_lag3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tot_agus2</t>
+          <t>gen_agus2_unit1_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag1</t>
+          <t>gen_agus2_unit1_lag6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag3</t>
+          <t>gen_agus2_unit1_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag6</t>
+          <t>gen_agus2_unit1_lag12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag12</t>
+          <t>gen_agus2_unit1_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag24</t>
+          <t>gen_agus2_unit1_lag24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>elev_agus2_lag1</t>
+          <t>gen_agus2_unit1_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>elev_agus2_lag3</t>
+          <t>gen_agus2_unit1_lag48</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>elev_agus2_lag6</t>
+          <t>gen_agus2_unit1_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>elev_agus2_lag12</t>
+          <t>gen_agus2_unit1_lag72</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>elev_agus2_lag24</t>
+          <t>gen_agus2_unit1_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>tot_agus2_lag1</t>
+          <t>gen_agus2_unit1_lag168</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>tot_agus2_lag3</t>
+          <t>gen_agus2_unit1_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tot_agus2_lag6</t>
+          <t>gen_agus2_unit2_current</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tot_agus2_lag12</t>
+          <t>gen_agus2_unit2_share_current</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tot_agus2_lag24</t>
+          <t>gen_agus2_unit2_lag1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag1</t>
+          <t>gen_agus2_unit2_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag3</t>
+          <t>gen_agus2_unit2_lag2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag6</t>
+          <t>gen_agus2_unit2_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag12</t>
+          <t>gen_agus2_unit2_lag3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag24</t>
+          <t>gen_agus2_unit2_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag1</t>
+          <t>gen_agus2_unit2_lag6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag3</t>
+          <t>gen_agus2_unit2_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag6</t>
+          <t>gen_agus2_unit2_lag12</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag12</t>
+          <t>gen_agus2_unit2_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag24</t>
+          <t>gen_agus2_unit2_lag24</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag1</t>
+          <t>gen_agus2_unit2_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag3</t>
+          <t>gen_agus2_unit2_lag48</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag6</t>
+          <t>gen_agus2_unit2_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag12</t>
+          <t>gen_agus2_unit2_lag72</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag24</t>
+          <t>gen_agus2_unit2_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag1</t>
+          <t>gen_agus2_unit2_lag168</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag3</t>
+          <t>gen_agus2_unit2_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag6</t>
+          <t>gen_agus2_unit3_current</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag12</t>
+          <t>gen_agus2_unit3_share_current</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag24</t>
+          <t>gen_agus2_unit3_lag1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag1</t>
+          <t>gen_agus2_unit3_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag3</t>
+          <t>gen_agus2_unit3_lag2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag6</t>
+          <t>gen_agus2_unit3_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag12</t>
+          <t>gen_agus2_unit3_lag3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag24</t>
+          <t>gen_agus2_unit3_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>elev_agus1_lag1</t>
+          <t>gen_agus2_unit3_lag6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>elev_agus1_lag3</t>
+          <t>gen_agus2_unit3_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>elev_agus1_lag6</t>
+          <t>gen_agus2_unit3_lag12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>elev_agus1_lag12</t>
+          <t>gen_agus2_unit3_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>elev_agus1_lag24</t>
+          <t>gen_agus2_unit3_lag24</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>elev_agus4_lag1</t>
+          <t>gen_agus2_unit3_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>elev_agus4_lag3</t>
+          <t>gen_agus2_unit3_lag48</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>elev_agus4_lag6</t>
+          <t>gen_agus2_unit3_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>elev_agus4_lag12</t>
+          <t>gen_agus2_unit3_lag72</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>elev_agus4_lag24</t>
+          <t>gen_agus2_unit3_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>elev_agus5_lag1</t>
+          <t>gen_agus2_unit3_lag168</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>elev_agus5_lag3</t>
+          <t>gen_agus2_unit3_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>elev_agus5_lag6</t>
+          <t>out_agus2_unit1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>elev_agus5_lag12</t>
+          <t>out_agus2_unit2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>elev_agus5_lag24</t>
+          <t>out_agus2_unit3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>elev_agus6_lag1</t>
+          <t>agus2_units_running</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>elev_agus6_lag3</t>
+          <t>agus2_plant_available</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>elev_agus6_lag6</t>
+          <t>tot_agus2_gate</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>elev_agus6_lag12</t>
+          <t>elev_agus2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>elev_agus6_lag24</t>
+          <t>tot_agus2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>elev_agus7_lag1</t>
+          <t>tot_agus2_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>elev_agus7_lag3</t>
+          <t>tot_agus2_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>elev_agus7_lag6</t>
+          <t>tot_agus2_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>elev_agus7_lag12</t>
+          <t>tot_agus2_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>elev_agus7_lag24</t>
+          <t>tot_agus2_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag1</t>
+          <t>elev_agus2_lag1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag3</t>
+          <t>elev_agus2_lag3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag6</t>
+          <t>elev_agus2_lag6</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag12</t>
+          <t>elev_agus2_lag12</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag24</t>
+          <t>elev_agus2_lag24</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tot_agus1_lag1</t>
+          <t>tot_agus2_lag1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tot_agus1_lag3</t>
+          <t>tot_agus2_lag3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tot_agus1_lag6</t>
+          <t>tot_agus2_lag6</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tot_agus1_lag12</t>
+          <t>tot_agus2_lag12</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tot_agus1_lag24</t>
+          <t>tot_agus2_lag24</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tot_agus4_lag1</t>
+          <t>tot_agus1_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tot_agus4_lag3</t>
+          <t>tot_agus1_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tot_agus4_lag6</t>
+          <t>tot_agus1_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tot_agus4_lag12</t>
+          <t>tot_agus1_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tot_agus4_lag24</t>
+          <t>tot_agus1_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tot_agus5_lag1</t>
+          <t>tot_agus4_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tot_agus5_lag3</t>
+          <t>tot_agus4_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tot_agus5_lag6</t>
+          <t>tot_agus4_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tot_agus5_lag12</t>
+          <t>tot_agus4_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tot_agus5_lag24</t>
+          <t>tot_agus4_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tot_agus6_lag1</t>
+          <t>tot_agus5_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tot_agus6_lag3</t>
+          <t>tot_agus5_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tot_agus6_lag6</t>
+          <t>tot_agus5_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tot_agus6_lag12</t>
+          <t>tot_agus5_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tot_agus6_lag24</t>
+          <t>tot_agus5_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tot_agus7_lag1</t>
+          <t>tot_agus6_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tot_agus7_lag3</t>
+          <t>tot_agus6_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tot_agus7_lag6</t>
+          <t>tot_agus6_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>tot_agus7_lag12</t>
+          <t>tot_agus6_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tot_agus7_lag24</t>
+          <t>tot_agus6_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+          <t>tot_agus7_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+          <t>tot_agus7_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+          <t>tot_agus7_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+          <t>tot_agus7_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>tot_agus7_gate_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>rainfall_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>rainfall_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>rainfall_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>rainfall_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>rainfall_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
           <t>lake_lanao_hourly_outflow_elev_agus7_lag24</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A170"/>
+  <autoFilter ref="A1:A235"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3183,7 +3953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A170"/>
+  <dimension ref="A1:A235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3626,761 +4396,1216 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>out_agus4_unit1</t>
+          <t>gen_agus4_unit1_current</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>out_agus4_unit2</t>
+          <t>gen_agus4_unit1_share_current</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>out_agus4_unit3</t>
+          <t>gen_agus4_unit1_lag1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>agus4_units_running</t>
+          <t>gen_agus4_unit1_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>agus4_plant_available</t>
+          <t>gen_agus4_unit1_lag2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tot_agus4_gate</t>
+          <t>gen_agus4_unit1_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>elev_agus4</t>
+          <t>gen_agus4_unit1_lag3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tot_agus4</t>
+          <t>gen_agus4_unit1_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag1</t>
+          <t>gen_agus4_unit1_lag6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag3</t>
+          <t>gen_agus4_unit1_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag6</t>
+          <t>gen_agus4_unit1_lag12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag12</t>
+          <t>gen_agus4_unit1_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag24</t>
+          <t>gen_agus4_unit1_lag24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>elev_agus4_lag1</t>
+          <t>gen_agus4_unit1_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>elev_agus4_lag3</t>
+          <t>gen_agus4_unit1_lag48</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>elev_agus4_lag6</t>
+          <t>gen_agus4_unit1_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>elev_agus4_lag12</t>
+          <t>gen_agus4_unit1_lag72</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>elev_agus4_lag24</t>
+          <t>gen_agus4_unit1_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>tot_agus4_lag1</t>
+          <t>gen_agus4_unit1_lag168</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>tot_agus4_lag3</t>
+          <t>gen_agus4_unit1_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tot_agus4_lag6</t>
+          <t>gen_agus4_unit2_current</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tot_agus4_lag12</t>
+          <t>gen_agus4_unit2_share_current</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tot_agus4_lag24</t>
+          <t>gen_agus4_unit2_lag1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag1</t>
+          <t>gen_agus4_unit2_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag3</t>
+          <t>gen_agus4_unit2_lag2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag6</t>
+          <t>gen_agus4_unit2_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag12</t>
+          <t>gen_agus4_unit2_lag3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag24</t>
+          <t>gen_agus4_unit2_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag1</t>
+          <t>gen_agus4_unit2_lag6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag3</t>
+          <t>gen_agus4_unit2_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag6</t>
+          <t>gen_agus4_unit2_lag12</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag12</t>
+          <t>gen_agus4_unit2_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag24</t>
+          <t>gen_agus4_unit2_lag24</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag1</t>
+          <t>gen_agus4_unit2_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag3</t>
+          <t>gen_agus4_unit2_lag48</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag6</t>
+          <t>gen_agus4_unit2_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag12</t>
+          <t>gen_agus4_unit2_lag72</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag24</t>
+          <t>gen_agus4_unit2_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag1</t>
+          <t>gen_agus4_unit2_lag168</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag3</t>
+          <t>gen_agus4_unit2_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag6</t>
+          <t>gen_agus4_unit3_current</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag12</t>
+          <t>gen_agus4_unit3_share_current</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag24</t>
+          <t>gen_agus4_unit3_lag1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag1</t>
+          <t>gen_agus4_unit3_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag3</t>
+          <t>gen_agus4_unit3_lag2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag6</t>
+          <t>gen_agus4_unit3_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag12</t>
+          <t>gen_agus4_unit3_lag3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag24</t>
+          <t>gen_agus4_unit3_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>elev_agus1_lag1</t>
+          <t>gen_agus4_unit3_lag6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>elev_agus1_lag3</t>
+          <t>gen_agus4_unit3_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>elev_agus1_lag6</t>
+          <t>gen_agus4_unit3_lag12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>elev_agus1_lag12</t>
+          <t>gen_agus4_unit3_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>elev_agus1_lag24</t>
+          <t>gen_agus4_unit3_lag24</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>elev_agus2_lag1</t>
+          <t>gen_agus4_unit3_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>elev_agus2_lag3</t>
+          <t>gen_agus4_unit3_lag48</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>elev_agus2_lag6</t>
+          <t>gen_agus4_unit3_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>elev_agus2_lag12</t>
+          <t>gen_agus4_unit3_lag72</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>elev_agus2_lag24</t>
+          <t>gen_agus4_unit3_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>elev_agus5_lag1</t>
+          <t>gen_agus4_unit3_lag168</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>elev_agus5_lag3</t>
+          <t>gen_agus4_unit3_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>elev_agus5_lag6</t>
+          <t>out_agus4_unit1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>elev_agus5_lag12</t>
+          <t>out_agus4_unit2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>elev_agus5_lag24</t>
+          <t>out_agus4_unit3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>elev_agus6_lag1</t>
+          <t>agus4_units_running</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>elev_agus6_lag3</t>
+          <t>agus4_plant_available</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>elev_agus6_lag6</t>
+          <t>tot_agus4_gate</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>elev_agus6_lag12</t>
+          <t>elev_agus4</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>elev_agus6_lag24</t>
+          <t>tot_agus4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>elev_agus7_lag1</t>
+          <t>tot_agus4_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>elev_agus7_lag3</t>
+          <t>tot_agus4_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>elev_agus7_lag6</t>
+          <t>tot_agus4_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>elev_agus7_lag12</t>
+          <t>tot_agus4_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>elev_agus7_lag24</t>
+          <t>tot_agus4_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag1</t>
+          <t>elev_agus4_lag1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag3</t>
+          <t>elev_agus4_lag3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag6</t>
+          <t>elev_agus4_lag6</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag12</t>
+          <t>elev_agus4_lag12</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag24</t>
+          <t>elev_agus4_lag24</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tot_agus1_lag1</t>
+          <t>tot_agus4_lag1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tot_agus1_lag3</t>
+          <t>tot_agus4_lag3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tot_agus1_lag6</t>
+          <t>tot_agus4_lag6</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tot_agus1_lag12</t>
+          <t>tot_agus4_lag12</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tot_agus1_lag24</t>
+          <t>tot_agus4_lag24</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tot_agus2_lag1</t>
+          <t>tot_agus1_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tot_agus2_lag3</t>
+          <t>tot_agus1_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tot_agus2_lag6</t>
+          <t>tot_agus1_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tot_agus2_lag12</t>
+          <t>tot_agus1_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tot_agus2_lag24</t>
+          <t>tot_agus1_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tot_agus5_lag1</t>
+          <t>tot_agus2_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tot_agus5_lag3</t>
+          <t>tot_agus2_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tot_agus5_lag6</t>
+          <t>tot_agus2_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tot_agus5_lag12</t>
+          <t>tot_agus2_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tot_agus5_lag24</t>
+          <t>tot_agus2_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tot_agus6_lag1</t>
+          <t>tot_agus5_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tot_agus6_lag3</t>
+          <t>tot_agus5_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tot_agus6_lag6</t>
+          <t>tot_agus5_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tot_agus6_lag12</t>
+          <t>tot_agus5_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tot_agus6_lag24</t>
+          <t>tot_agus5_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tot_agus7_lag1</t>
+          <t>tot_agus6_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tot_agus7_lag3</t>
+          <t>tot_agus6_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tot_agus7_lag6</t>
+          <t>tot_agus6_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>tot_agus7_lag12</t>
+          <t>tot_agus6_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tot_agus7_lag24</t>
+          <t>tot_agus6_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+          <t>tot_agus7_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+          <t>tot_agus7_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+          <t>tot_agus7_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+          <t>tot_agus7_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>tot_agus7_gate_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>rainfall_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>rainfall_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>rainfall_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>rainfall_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>rainfall_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
           <t>lake_lanao_hourly_outflow_elev_agus7_lag24</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A170"/>
+  <autoFilter ref="A1:A235"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4391,7 +5616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A169"/>
+  <dimension ref="A1:A214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4834,754 +6059,1069 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>out_agus5_unit1</t>
+          <t>gen_agus5_unit1_current</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>out_agus5_unit2</t>
+          <t>gen_agus5_unit1_share_current</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>agus5_units_running</t>
+          <t>gen_agus5_unit1_lag1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>agus5_plant_available</t>
+          <t>gen_agus5_unit1_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tot_agus5_gate</t>
+          <t>gen_agus5_unit1_lag2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>elev_agus5</t>
+          <t>gen_agus5_unit1_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tot_agus5</t>
+          <t>gen_agus5_unit1_lag3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag1</t>
+          <t>gen_agus5_unit1_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag3</t>
+          <t>gen_agus5_unit1_lag6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag6</t>
+          <t>gen_agus5_unit1_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag12</t>
+          <t>gen_agus5_unit1_lag12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag24</t>
+          <t>gen_agus5_unit1_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>elev_agus5_lag1</t>
+          <t>gen_agus5_unit1_lag24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>elev_agus5_lag3</t>
+          <t>gen_agus5_unit1_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>elev_agus5_lag6</t>
+          <t>gen_agus5_unit1_lag48</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>elev_agus5_lag12</t>
+          <t>gen_agus5_unit1_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>elev_agus5_lag24</t>
+          <t>gen_agus5_unit1_lag72</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>tot_agus5_lag1</t>
+          <t>gen_agus5_unit1_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>tot_agus5_lag3</t>
+          <t>gen_agus5_unit1_lag168</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>tot_agus5_lag6</t>
+          <t>gen_agus5_unit1_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tot_agus5_lag12</t>
+          <t>gen_agus5_unit2_current</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tot_agus5_lag24</t>
+          <t>gen_agus5_unit2_share_current</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag1</t>
+          <t>gen_agus5_unit2_lag1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag3</t>
+          <t>gen_agus5_unit2_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag6</t>
+          <t>gen_agus5_unit2_lag2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag12</t>
+          <t>gen_agus5_unit2_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag24</t>
+          <t>gen_agus5_unit2_lag3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag1</t>
+          <t>gen_agus5_unit2_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag3</t>
+          <t>gen_agus5_unit2_lag6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag6</t>
+          <t>gen_agus5_unit2_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag12</t>
+          <t>gen_agus5_unit2_lag12</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag24</t>
+          <t>gen_agus5_unit2_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag1</t>
+          <t>gen_agus5_unit2_lag24</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag3</t>
+          <t>gen_agus5_unit2_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag6</t>
+          <t>gen_agus5_unit2_lag48</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag12</t>
+          <t>gen_agus5_unit2_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag24</t>
+          <t>gen_agus5_unit2_lag72</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag1</t>
+          <t>gen_agus5_unit2_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag3</t>
+          <t>gen_agus5_unit2_lag168</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag6</t>
+          <t>gen_agus5_unit2_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag12</t>
+          <t>out_agus5_unit1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag24</t>
+          <t>out_agus5_unit2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag1</t>
+          <t>agus5_units_running</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag3</t>
+          <t>agus5_plant_available</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag6</t>
+          <t>tot_agus5_gate</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag12</t>
+          <t>elev_agus5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag24</t>
+          <t>tot_agus5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>elev_agus1_lag1</t>
+          <t>tot_agus5_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>elev_agus1_lag3</t>
+          <t>tot_agus5_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>elev_agus1_lag6</t>
+          <t>tot_agus5_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>elev_agus1_lag12</t>
+          <t>tot_agus5_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>elev_agus1_lag24</t>
+          <t>tot_agus5_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>elev_agus2_lag1</t>
+          <t>elev_agus5_lag1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>elev_agus2_lag3</t>
+          <t>elev_agus5_lag3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>elev_agus2_lag6</t>
+          <t>elev_agus5_lag6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>elev_agus2_lag12</t>
+          <t>elev_agus5_lag12</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>elev_agus2_lag24</t>
+          <t>elev_agus5_lag24</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>elev_agus4_lag1</t>
+          <t>tot_agus5_lag1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>elev_agus4_lag3</t>
+          <t>tot_agus5_lag3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>elev_agus4_lag6</t>
+          <t>tot_agus5_lag6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>elev_agus4_lag12</t>
+          <t>tot_agus5_lag12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>elev_agus4_lag24</t>
+          <t>tot_agus5_lag24</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>elev_agus6_lag1</t>
+          <t>tot_agus1_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>elev_agus6_lag3</t>
+          <t>tot_agus1_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>elev_agus6_lag6</t>
+          <t>tot_agus1_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>elev_agus6_lag12</t>
+          <t>tot_agus1_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>elev_agus6_lag24</t>
+          <t>tot_agus1_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>elev_agus7_lag1</t>
+          <t>tot_agus2_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>elev_agus7_lag3</t>
+          <t>tot_agus2_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>elev_agus7_lag6</t>
+          <t>tot_agus2_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>elev_agus7_lag12</t>
+          <t>tot_agus2_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>elev_agus7_lag24</t>
+          <t>tot_agus2_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag1</t>
+          <t>tot_agus4_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag3</t>
+          <t>tot_agus4_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag6</t>
+          <t>tot_agus4_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag12</t>
+          <t>tot_agus4_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag24</t>
+          <t>tot_agus4_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>tot_agus1_lag1</t>
+          <t>tot_agus6_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tot_agus1_lag3</t>
+          <t>tot_agus6_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tot_agus1_lag6</t>
+          <t>tot_agus6_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tot_agus1_lag12</t>
+          <t>tot_agus6_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tot_agus1_lag24</t>
+          <t>tot_agus6_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tot_agus2_lag1</t>
+          <t>tot_agus7_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tot_agus2_lag3</t>
+          <t>tot_agus7_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tot_agus2_lag6</t>
+          <t>tot_agus7_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tot_agus2_lag12</t>
+          <t>tot_agus7_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tot_agus2_lag24</t>
+          <t>tot_agus7_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tot_agus4_lag1</t>
+          <t>elev_agus1_lag1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tot_agus4_lag3</t>
+          <t>elev_agus1_lag3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tot_agus4_lag6</t>
+          <t>elev_agus1_lag6</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tot_agus4_lag12</t>
+          <t>elev_agus1_lag12</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tot_agus4_lag24</t>
+          <t>elev_agus1_lag24</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tot_agus6_lag1</t>
+          <t>elev_agus2_lag1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tot_agus6_lag3</t>
+          <t>elev_agus2_lag3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tot_agus6_lag6</t>
+          <t>elev_agus2_lag6</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tot_agus6_lag12</t>
+          <t>elev_agus2_lag12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tot_agus6_lag24</t>
+          <t>elev_agus2_lag24</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tot_agus7_lag1</t>
+          <t>elev_agus4_lag1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tot_agus7_lag3</t>
+          <t>elev_agus4_lag3</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tot_agus7_lag6</t>
+          <t>elev_agus4_lag6</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tot_agus7_lag12</t>
+          <t>elev_agus4_lag12</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>tot_agus7_lag24</t>
+          <t>elev_agus4_lag24</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+          <t>elev_agus6_lag1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+          <t>elev_agus6_lag3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+          <t>elev_agus6_lag6</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+          <t>elev_agus6_lag12</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t>elev_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>rainfall_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>rainfall_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>rainfall_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>rainfall_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>rainfall_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>lake_lanao_hourly_outflow_elev_agus7_lag24</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A169"/>
+  <autoFilter ref="A1:A214"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5592,7 +7132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A172"/>
+  <dimension ref="A1:A277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6035,775 +7575,1510 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>out_agus6_unit1</t>
+          <t>gen_agus6_unit1_current</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>out_agus6_unit2</t>
+          <t>gen_agus6_unit1_share_current</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>out_agus6_unit3</t>
+          <t>gen_agus6_unit1_lag1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>out_agus6_unit4</t>
+          <t>gen_agus6_unit1_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>out_agus6_unit5</t>
+          <t>gen_agus6_unit1_lag2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>agus6_units_running</t>
+          <t>gen_agus6_unit1_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>agus6_plant_available</t>
+          <t>gen_agus6_unit1_lag3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tot_agus6_gate</t>
+          <t>gen_agus6_unit1_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>elev_agus6</t>
+          <t>gen_agus6_unit1_lag6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tot_agus6</t>
+          <t>gen_agus6_unit1_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag1</t>
+          <t>gen_agus6_unit1_lag12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag3</t>
+          <t>gen_agus6_unit1_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag6</t>
+          <t>gen_agus6_unit1_lag24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag12</t>
+          <t>gen_agus6_unit1_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag24</t>
+          <t>gen_agus6_unit1_lag48</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>elev_agus6_lag1</t>
+          <t>gen_agus6_unit1_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>elev_agus6_lag3</t>
+          <t>gen_agus6_unit1_lag72</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>elev_agus6_lag6</t>
+          <t>gen_agus6_unit1_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>elev_agus6_lag12</t>
+          <t>gen_agus6_unit1_lag168</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>elev_agus6_lag24</t>
+          <t>gen_agus6_unit1_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tot_agus6_lag1</t>
+          <t>gen_agus6_unit2_current</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tot_agus6_lag3</t>
+          <t>gen_agus6_unit2_share_current</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tot_agus6_lag6</t>
+          <t>gen_agus6_unit2_lag1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tot_agus6_lag12</t>
+          <t>gen_agus6_unit2_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tot_agus6_lag24</t>
+          <t>gen_agus6_unit2_lag2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag1</t>
+          <t>gen_agus6_unit2_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag3</t>
+          <t>gen_agus6_unit2_lag3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag6</t>
+          <t>gen_agus6_unit2_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag12</t>
+          <t>gen_agus6_unit2_lag6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag24</t>
+          <t>gen_agus6_unit2_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag1</t>
+          <t>gen_agus6_unit2_lag12</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag3</t>
+          <t>gen_agus6_unit2_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag6</t>
+          <t>gen_agus6_unit2_lag24</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag12</t>
+          <t>gen_agus6_unit2_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag24</t>
+          <t>gen_agus6_unit2_lag48</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag1</t>
+          <t>gen_agus6_unit2_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag3</t>
+          <t>gen_agus6_unit2_lag72</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag6</t>
+          <t>gen_agus6_unit2_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag12</t>
+          <t>gen_agus6_unit2_lag168</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag24</t>
+          <t>gen_agus6_unit2_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag1</t>
+          <t>gen_agus6_unit3_current</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag3</t>
+          <t>gen_agus6_unit3_share_current</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag6</t>
+          <t>gen_agus6_unit3_lag1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag12</t>
+          <t>gen_agus6_unit3_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag24</t>
+          <t>gen_agus6_unit3_lag2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag1</t>
+          <t>gen_agus6_unit3_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag3</t>
+          <t>gen_agus6_unit3_lag3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag6</t>
+          <t>gen_agus6_unit3_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag12</t>
+          <t>gen_agus6_unit3_lag6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag24</t>
+          <t>gen_agus6_unit3_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>elev_agus1_lag1</t>
+          <t>gen_agus6_unit3_lag12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>elev_agus1_lag3</t>
+          <t>gen_agus6_unit3_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>elev_agus1_lag6</t>
+          <t>gen_agus6_unit3_lag24</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>elev_agus1_lag12</t>
+          <t>gen_agus6_unit3_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>elev_agus1_lag24</t>
+          <t>gen_agus6_unit3_lag48</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>elev_agus2_lag1</t>
+          <t>gen_agus6_unit3_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>elev_agus2_lag3</t>
+          <t>gen_agus6_unit3_lag72</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>elev_agus2_lag6</t>
+          <t>gen_agus6_unit3_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>elev_agus2_lag12</t>
+          <t>gen_agus6_unit3_lag168</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>elev_agus2_lag24</t>
+          <t>gen_agus6_unit3_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>elev_agus4_lag1</t>
+          <t>gen_agus6_unit4_current</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>elev_agus4_lag3</t>
+          <t>gen_agus6_unit4_share_current</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>elev_agus4_lag6</t>
+          <t>gen_agus6_unit4_lag1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>elev_agus4_lag12</t>
+          <t>gen_agus6_unit4_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>elev_agus4_lag24</t>
+          <t>gen_agus6_unit4_lag2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>elev_agus5_lag1</t>
+          <t>gen_agus6_unit4_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>elev_agus5_lag3</t>
+          <t>gen_agus6_unit4_lag3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>elev_agus5_lag6</t>
+          <t>gen_agus6_unit4_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>elev_agus5_lag12</t>
+          <t>gen_agus6_unit4_lag6</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>elev_agus5_lag24</t>
+          <t>gen_agus6_unit4_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>elev_agus7_lag1</t>
+          <t>gen_agus6_unit4_lag12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>elev_agus7_lag3</t>
+          <t>gen_agus6_unit4_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>elev_agus7_lag6</t>
+          <t>gen_agus6_unit4_lag24</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>elev_agus7_lag12</t>
+          <t>gen_agus6_unit4_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>elev_agus7_lag24</t>
+          <t>gen_agus6_unit4_lag48</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag1</t>
+          <t>gen_agus6_unit4_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag3</t>
+          <t>gen_agus6_unit4_lag72</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag6</t>
+          <t>gen_agus6_unit4_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag12</t>
+          <t>gen_agus6_unit4_lag168</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag24</t>
+          <t>gen_agus6_unit4_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tot_agus1_lag1</t>
+          <t>gen_agus6_unit5_current</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tot_agus1_lag3</t>
+          <t>gen_agus6_unit5_share_current</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tot_agus1_lag6</t>
+          <t>gen_agus6_unit5_lag1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tot_agus1_lag12</t>
+          <t>gen_agus6_unit5_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tot_agus1_lag24</t>
+          <t>gen_agus6_unit5_lag2</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tot_agus2_lag1</t>
+          <t>gen_agus6_unit5_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tot_agus2_lag3</t>
+          <t>gen_agus6_unit5_lag3</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tot_agus2_lag6</t>
+          <t>gen_agus6_unit5_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tot_agus2_lag12</t>
+          <t>gen_agus6_unit5_lag6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tot_agus2_lag24</t>
+          <t>gen_agus6_unit5_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tot_agus4_lag1</t>
+          <t>gen_agus6_unit5_lag12</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tot_agus4_lag3</t>
+          <t>gen_agus6_unit5_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tot_agus4_lag6</t>
+          <t>gen_agus6_unit5_lag24</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tot_agus4_lag12</t>
+          <t>gen_agus6_unit5_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tot_agus4_lag24</t>
+          <t>gen_agus6_unit5_lag48</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tot_agus5_lag1</t>
+          <t>gen_agus6_unit5_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tot_agus5_lag3</t>
+          <t>gen_agus6_unit5_lag72</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tot_agus5_lag6</t>
+          <t>gen_agus6_unit5_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tot_agus5_lag12</t>
+          <t>gen_agus6_unit5_lag168</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tot_agus5_lag24</t>
+          <t>gen_agus6_unit5_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tot_agus7_lag1</t>
+          <t>out_agus6_unit1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>tot_agus7_lag3</t>
+          <t>out_agus6_unit2</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tot_agus7_lag6</t>
+          <t>out_agus6_unit3</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>tot_agus7_lag12</t>
+          <t>out_agus6_unit4</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tot_agus7_lag24</t>
+          <t>out_agus6_unit5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+          <t>agus6_units_running</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+          <t>agus6_plant_available</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+          <t>tot_agus6_gate</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+          <t>elev_agus6</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>tot_agus6</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>tot_agus6_gate_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>tot_agus6_gate_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>tot_agus6_gate_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>tot_agus6_gate_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>tot_agus6_gate_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>tot_agus1_gate_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>tot_agus1_gate_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>tot_agus1_gate_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>tot_agus1_gate_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>tot_agus1_gate_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>tot_agus2_gate_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>tot_agus2_gate_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>tot_agus2_gate_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>tot_agus2_gate_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>tot_agus2_gate_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>tot_agus4_gate_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tot_agus4_gate_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>tot_agus4_gate_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>tot_agus4_gate_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>tot_agus4_gate_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>tot_agus5_gate_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>tot_agus5_gate_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>tot_agus5_gate_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>tot_agus5_gate_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>tot_agus5_gate_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>tot_agus7_gate_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>tot_agus7_gate_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>tot_agus7_gate_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>tot_agus7_gate_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>tot_agus7_gate_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>elev_agus1_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>elev_agus2_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>elev_agus4_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>elev_agus5_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>elev_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>rainfall_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>rainfall_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>rainfall_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>rainfall_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>rainfall_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>tot_agus7_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
           <t>lake_lanao_hourly_outflow_elev_agus7_lag24</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A172"/>
+  <autoFilter ref="A1:A277"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6814,7 +9089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A169"/>
+  <dimension ref="A1:A214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -7257,754 +9532,1069 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>out_agus7_unit1</t>
+          <t>gen_agus7_unit1_current</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>out_agus7_unit2</t>
+          <t>gen_agus7_unit1_share_current</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>agus7_units_running</t>
+          <t>gen_agus7_unit1_lag1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>agus7_plant_available</t>
+          <t>gen_agus7_unit1_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tot_agus7_gate</t>
+          <t>gen_agus7_unit1_lag2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>elev_agus7</t>
+          <t>gen_agus7_unit1_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tot_agus7</t>
+          <t>gen_agus7_unit1_lag3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag1</t>
+          <t>gen_agus7_unit1_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag3</t>
+          <t>gen_agus7_unit1_lag6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag6</t>
+          <t>gen_agus7_unit1_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag12</t>
+          <t>gen_agus7_unit1_lag12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tot_agus7_gate_lag24</t>
+          <t>gen_agus7_unit1_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>elev_agus7_lag1</t>
+          <t>gen_agus7_unit1_lag24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>elev_agus7_lag3</t>
+          <t>gen_agus7_unit1_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>elev_agus7_lag6</t>
+          <t>gen_agus7_unit1_lag48</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>elev_agus7_lag12</t>
+          <t>gen_agus7_unit1_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>elev_agus7_lag24</t>
+          <t>gen_agus7_unit1_lag72</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>tot_agus7_lag1</t>
+          <t>gen_agus7_unit1_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>tot_agus7_lag3</t>
+          <t>gen_agus7_unit1_lag168</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>tot_agus7_lag6</t>
+          <t>gen_agus7_unit1_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tot_agus7_lag12</t>
+          <t>gen_agus7_unit2_current</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tot_agus7_lag24</t>
+          <t>gen_agus7_unit2_share_current</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag1</t>
+          <t>gen_agus7_unit2_lag1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag3</t>
+          <t>gen_agus7_unit2_share_lag1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag6</t>
+          <t>gen_agus7_unit2_lag2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag12</t>
+          <t>gen_agus7_unit2_share_lag2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tot_agus1_gate_lag24</t>
+          <t>gen_agus7_unit2_lag3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag1</t>
+          <t>gen_agus7_unit2_share_lag3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag3</t>
+          <t>gen_agus7_unit2_lag6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag6</t>
+          <t>gen_agus7_unit2_share_lag6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag12</t>
+          <t>gen_agus7_unit2_lag12</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tot_agus2_gate_lag24</t>
+          <t>gen_agus7_unit2_share_lag12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag1</t>
+          <t>gen_agus7_unit2_lag24</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag3</t>
+          <t>gen_agus7_unit2_share_lag24</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag6</t>
+          <t>gen_agus7_unit2_lag48</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag12</t>
+          <t>gen_agus7_unit2_share_lag48</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>tot_agus4_gate_lag24</t>
+          <t>gen_agus7_unit2_lag72</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag1</t>
+          <t>gen_agus7_unit2_share_lag72</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag3</t>
+          <t>gen_agus7_unit2_lag168</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag6</t>
+          <t>gen_agus7_unit2_share_lag168</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag12</t>
+          <t>out_agus7_unit1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>tot_agus5_gate_lag24</t>
+          <t>out_agus7_unit2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag1</t>
+          <t>agus7_units_running</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag3</t>
+          <t>agus7_plant_available</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag6</t>
+          <t>tot_agus7_gate</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag12</t>
+          <t>elev_agus7</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tot_agus6_gate_lag24</t>
+          <t>tot_agus7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>elev_agus1_lag1</t>
+          <t>tot_agus7_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>elev_agus1_lag3</t>
+          <t>tot_agus7_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>elev_agus1_lag6</t>
+          <t>tot_agus7_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>elev_agus1_lag12</t>
+          <t>tot_agus7_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>elev_agus1_lag24</t>
+          <t>tot_agus7_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>elev_agus2_lag1</t>
+          <t>elev_agus7_lag1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>elev_agus2_lag3</t>
+          <t>elev_agus7_lag3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>elev_agus2_lag6</t>
+          <t>elev_agus7_lag6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>elev_agus2_lag12</t>
+          <t>elev_agus7_lag12</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>elev_agus2_lag24</t>
+          <t>elev_agus7_lag24</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>elev_agus4_lag1</t>
+          <t>tot_agus7_lag1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>elev_agus4_lag3</t>
+          <t>tot_agus7_lag3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>elev_agus4_lag6</t>
+          <t>tot_agus7_lag6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>elev_agus4_lag12</t>
+          <t>tot_agus7_lag12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>elev_agus4_lag24</t>
+          <t>tot_agus7_lag24</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>elev_agus5_lag1</t>
+          <t>tot_agus1_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>elev_agus5_lag3</t>
+          <t>tot_agus1_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>elev_agus5_lag6</t>
+          <t>tot_agus1_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>elev_agus5_lag12</t>
+          <t>tot_agus1_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>elev_agus5_lag24</t>
+          <t>tot_agus1_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>elev_agus6_lag1</t>
+          <t>tot_agus2_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>elev_agus6_lag3</t>
+          <t>tot_agus2_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>elev_agus6_lag6</t>
+          <t>tot_agus2_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>elev_agus6_lag12</t>
+          <t>tot_agus2_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>elev_agus6_lag24</t>
+          <t>tot_agus2_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag1</t>
+          <t>tot_agus4_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag3</t>
+          <t>tot_agus4_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag6</t>
+          <t>tot_agus4_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag12</t>
+          <t>tot_agus4_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lake_lanao_outflow_lag24</t>
+          <t>tot_agus4_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>tot_agus1_lag1</t>
+          <t>tot_agus5_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tot_agus1_lag3</t>
+          <t>tot_agus5_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tot_agus1_lag6</t>
+          <t>tot_agus5_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tot_agus1_lag12</t>
+          <t>tot_agus5_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tot_agus1_lag24</t>
+          <t>tot_agus5_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tot_agus2_lag1</t>
+          <t>tot_agus6_gate_lag1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tot_agus2_lag3</t>
+          <t>tot_agus6_gate_lag3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tot_agus2_lag6</t>
+          <t>tot_agus6_gate_lag6</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tot_agus2_lag12</t>
+          <t>tot_agus6_gate_lag12</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tot_agus2_lag24</t>
+          <t>tot_agus6_gate_lag24</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tot_agus4_lag1</t>
+          <t>elev_agus1_lag1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tot_agus4_lag3</t>
+          <t>elev_agus1_lag3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tot_agus4_lag6</t>
+          <t>elev_agus1_lag6</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tot_agus4_lag12</t>
+          <t>elev_agus1_lag12</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tot_agus4_lag24</t>
+          <t>elev_agus1_lag24</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tot_agus5_lag1</t>
+          <t>elev_agus2_lag1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tot_agus5_lag3</t>
+          <t>elev_agus2_lag3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tot_agus5_lag6</t>
+          <t>elev_agus2_lag6</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tot_agus5_lag12</t>
+          <t>elev_agus2_lag12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tot_agus5_lag24</t>
+          <t>elev_agus2_lag24</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tot_agus6_lag1</t>
+          <t>elev_agus4_lag1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tot_agus6_lag3</t>
+          <t>elev_agus4_lag3</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tot_agus6_lag6</t>
+          <t>elev_agus4_lag6</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tot_agus6_lag12</t>
+          <t>elev_agus4_lag12</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>tot_agus6_lag24</t>
+          <t>elev_agus4_lag24</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+          <t>elev_agus5_lag1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+          <t>elev_agus5_lag3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+          <t>elev_agus5_lag6</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+          <t>elev_agus5_lag12</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t>elev_agus5_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>elev_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>lake_lanao_outflow_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>rainfall_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>rainfall_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>rainfall_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>rainfall_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>rainfall_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>tot_agus1_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>tot_agus2_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tot_agus4_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>tot_agus5_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>tot_agus6_lag24</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag3</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag6</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>lake_lanao_hourly_outflow_elev_agus7_lag12</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>lake_lanao_hourly_outflow_elev_agus7_lag24</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A169"/>
+  <autoFilter ref="A1:A214"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>